--- a/data/trans_dic/P1414-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1414-Edad-trans_dic.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,47</t>
+          <t>0,0; 0,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -793,27 +793,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,5</t>
+          <t>0,16; 1,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,86</t>
+          <t>0,17; 1,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,39</t>
+          <t>0,16; 1,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 1,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,04</t>
+          <t>0,17; 1,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,76</t>
+          <t>0,09; 0,89</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -913,32 +913,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,38</t>
+          <t>1,24; 3,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,3</t>
+          <t>0,55; 2,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,18</t>
+          <t>1,07; 2,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,78</t>
+          <t>0,63; 1,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,2</t>
+          <t>0,26; 1,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,6</t>
+          <t>0,52; 1,44</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,56</t>
+          <t>0,17; 1,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,6</t>
+          <t>0,17; 1,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 6,13</t>
+          <t>2,56; 5,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,82</t>
+          <t>3,95; 7,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,1</t>
+          <t>2,96; 5,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,14</t>
+          <t>1,46; 3,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,28</t>
+          <t>2,31; 4,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,75</t>
+          <t>1,79; 3,21</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1123,42 +1123,42 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,24</t>
+          <t>0,25; 2,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,71</t>
+          <t>0,26; 1,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,41; 9,18</t>
+          <t>4,2; 9,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,44; 11,78</t>
+          <t>6,39; 11,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,95; 10,48</t>
+          <t>6,63; 10,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,11</t>
+          <t>2,32; 4,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 6,48</t>
+          <t>3,75; 6,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,66; 5,5</t>
+          <t>3,7; 5,52</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 3,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,9</t>
+          <t>0,26; 1,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,36</t>
+          <t>1,7; 5,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,46; 8,15</t>
+          <t>3,58; 8,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,93; 9,64</t>
+          <t>7,17; 11,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,17</t>
+          <t>1,07; 3,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,89</t>
+          <t>2,07; 4,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,49</t>
+          <t>4,01; 6,29</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1348,37 +1348,37 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,29</t>
+          <t>1,13; 4,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 5,1</t>
+          <t>1,3; 5,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,83</t>
+          <t>3,08; 6,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,89</t>
+          <t>0,7; 2,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,35</t>
+          <t>0,78; 3,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,56</t>
+          <t>1,99; 3,73</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1453,42 +1453,42 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,74</t>
+          <t>0,23; 0,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,72</t>
+          <t>0,25; 0,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,19</t>
+          <t>2,1; 3,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,92; 4,19</t>
+          <t>2,95; 4,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,08; 4,43</t>
+          <t>3,69; 4,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,75</t>
+          <t>1,16; 1,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,38</t>
+          <t>1,7; 2,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,49</t>
+          <t>2,06; 2,62</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>2032</t>
         </is>
       </c>
     </row>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4555</t>
+          <t>0; 5171</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 8892</t>
+          <t>0; 10175</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1785,12 +1785,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3831</t>
+          <t>0; 4814</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 9864</t>
+          <t>0; 11862</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>3160</t>
         </is>
       </c>
     </row>
@@ -1918,42 +1918,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>960; 8848</t>
+          <t>965; 8687</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5351</t>
+          <t>0; 7436</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1037; 11336</t>
+          <t>1041; 11580</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>910; 7846</t>
+          <t>916; 8746</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5234</t>
+          <t>0; 6237</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1037; 11464</t>
+          <t>1046; 11442</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2039; 12048</t>
+          <t>2002; 12034</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>159; 7066</t>
+          <t>878; 8676</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>11760</t>
         </is>
       </c>
     </row>
@@ -2091,32 +2091,32 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8050; 24014</t>
+          <t>8833; 24160</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3487; 15189</t>
+          <t>3649; 15221</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6235; 17195</t>
+          <t>6620; 18287</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8278; 24723</t>
+          <t>8716; 24104</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3496; 15932</t>
+          <t>3514; 15797</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6504; 17166</t>
+          <t>6498; 17803</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5241</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26873</t>
+          <t>29143</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>32113</t>
+          <t>34581</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 7021</t>
+          <t>0; 7151</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1082; 10106</t>
+          <t>1092; 10508</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1033; 14161</t>
+          <t>1175; 13839</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16065; 37643</t>
+          <t>15738; 35956</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26076; 50754</t>
+          <t>25627; 51024</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19477; 36203</t>
+          <t>21662; 38507</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17191; 38554</t>
+          <t>17963; 38384</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29818; 55447</t>
+          <t>29876; 57368</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18309; 43940</t>
+          <t>25624; 45937</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45634</t>
+          <t>50625</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>49949</t>
+          <t>54993</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 7472</t>
+          <t>0; 7475</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1191; 10686</t>
+          <t>1195; 10658</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1622; 9547</t>
+          <t>1610; 10035</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19740; 41099</t>
+          <t>18798; 40609</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32017; 58508</t>
+          <t>31752; 57828</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37647; 56736</t>
+          <t>39936; 62574</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21575; 44827</t>
+          <t>20373; 43365</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>35102; 63129</t>
+          <t>36505; 63009</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40289; 60518</t>
+          <t>44801; 66797</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35702</t>
+          <t>39257</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>38670</t>
+          <t>42331</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 7551</t>
+          <t>0; 7605</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 8993</t>
+          <t>0; 10381</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1054; 6940</t>
+          <t>1051; 6779</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5872; 18905</t>
+          <t>5984; 19259</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13052; 30797</t>
+          <t>13522; 31529</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11687; 58388</t>
+          <t>31273; 48260</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6883; 21029</t>
+          <t>7113; 21261</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14647; 34794</t>
+          <t>14716; 34314</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20086; 53327</t>
+          <t>33697; 52901</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>521</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18104</t>
+          <t>20330</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>18618</t>
+          <t>20851</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5322</t>
+          <t>0; 4279</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2738,37 +2738,37 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 2586</t>
+          <t>0; 3106</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4400; 16675</t>
+          <t>4391; 16998</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5133; 20425</t>
+          <t>5186; 20414</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13015; 24778</t>
+          <t>14278; 28188</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4503; 18483</t>
+          <t>4450; 17634</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6154; 22022</t>
+          <t>5150; 20575</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13180; 25170</t>
+          <t>15334; 28788</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>139611</t>
+          <t>154942</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>153915</t>
+          <t>169709</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3156; 14751</t>
+          <t>3101; 14843</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>7736; 24968</t>
+          <t>7964; 23343</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8274; 24721</t>
+          <t>8751; 24926</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>74465; 113465</t>
+          <t>74492; 112317</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>103445; 148355</t>
+          <t>104683; 152413</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>112384; 161418</t>
+          <t>137214; 175174</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>81633; 122298</t>
+          <t>80983; 122212</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>117704; 165178</t>
+          <t>118219; 163638</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>129157; 176545</t>
+          <t>149484; 190076</t>
         </is>
       </c>
     </row>
